--- a/event_planner_forms/004_virtual_job_fair_registration_form--event_planner_forms.xlsx
+++ b/event_planner_forms/004_virtual_job_fair_registration_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>attendee_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Attendee Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,19 +543,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>attendee_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Your Name</t>
-        </is>
-      </c>
+          <t>Attendee Email</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -570,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -593,64 +589,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>company_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Company Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>company_address</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Company Address</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -662,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_description</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Description</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_requirements</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Requirements</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>company_contact_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Company Contact Name</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>company_contact_email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Company Contact Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>exhibitor_or_job_seeker</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>Are you an exhibitor or a job seeker?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -777,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>job_requirements</t>
+          <t>organization_name</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Job Requirements</t>
+          <t>Organization Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -800,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>job_requirements</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Job Requirements</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>job_requirements</t>
+          <t>job_role</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Job Requirements</t>
+          <t>Job Role</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -846,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>job_title_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -869,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>job_description_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>Job Description 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -892,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>job_requirements</t>
+          <t>job_requirements_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Job Requirements</t>
+          <t>Job Requirements 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -915,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>additional_comments_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Job Description</t>
+          <t>Additional Comments 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>job_requirements</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Job Requirements</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>job_requirements</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Job Requirements</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>job_requirements</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Job Requirements</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>job_requirements</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Job Requirements</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>job_description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Job Description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>job_requirements</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Job Requirements</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>job_description</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Job Description</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'ceo',_'value':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'CEO', 'value': 'CEO'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -1152,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing_manager',_'value':_'marketing_manager'}</t>
+          <t>marketing_manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing Manager', 'value': 'Marketing Manager'}</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1004,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'intern',_'value':_'intern'}</t>
+          <t>intern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Intern', 'value': 'Intern'}</t>
+          <t>Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>exhibitor_or_job_seeker_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>exhibitor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Exhibitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>exhibitor_or_job_seeker_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>job_seeker</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Job Seeker</t>
         </is>
       </c>
     </row>
